--- a/EndResult/100m Fri.xlsx
+++ b/EndResult/100m Fri.xlsx
@@ -1273,25 +1273,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Karoline Volden</t>
+          <t>Maria Erikovna Alvestad</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58,61</t>
+          <t>56,21</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>630</v>
+        <v>714</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>17.11.2017</t>
+          <t>30.11.2025</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Kristiansand</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1308,25 +1308,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Maria Erikovna Alvestad</t>
+          <t>Karoline Volden</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>59,43</t>
+          <t>58,61</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>604</v>
+        <v>630</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>27.01.2024</t>
+          <t>17.11.2017</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansand</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">

--- a/EndResult/100m Fri.xlsx
+++ b/EndResult/100m Fri.xlsx
@@ -646,25 +646,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Simen Dahl Stensaas</t>
+          <t>Gabriel Rognes Steen</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>53,69</t>
+          <t>53,53</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>21.11.2015</t>
+          <t>13.06.2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -681,25 +681,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ole Skuseth</t>
+          <t>Simen Dahl Stensaas</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>53,76</t>
+          <t>53,69</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>29.10.2023</t>
+          <t>21.11.2015</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stavanger</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -716,25 +716,25 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ole Peder Uthus Solum</t>
+          <t>Ole Skuseth</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>54,03</t>
+          <t>53,76</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>571</v>
+        <v>580</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>19.01.2019</t>
+          <t>29.10.2023</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stavanger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -751,25 +751,25 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bjørnar Evensen</t>
+          <t>Thomas Trøite</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>54,08</t>
+          <t>53,95</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>03.03.2005</t>
+          <t>13.06.2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Stavanger</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -786,20 +786,20 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Odin Spangen Normann</t>
+          <t>Ole Peder Uthus Solum</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>54,05</t>
+          <t>54,03</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>19.01.2014</t>
+          <t>19.01.2019</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1117,20 +1117,20 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Christoffer Solberg Jørgensen</t>
+          <t>Gabriel Rognes Steen</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>55,49</t>
+          <t>55,36</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>02.03.2014</t>
+          <t>07.05.2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1152,25 +1152,25 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ole Peder Uthus Solum</t>
+          <t>Christoffer Solberg Jørgensen</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>55,52</t>
+          <t>55,49</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>05.04.2019</t>
+          <t>02.03.2014</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bergen</t>
+          <t>Berlin</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1187,25 +1187,25 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Leo Petter Hauge Sølvberg</t>
+          <t>Thomas Trøite</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>55,83</t>
+          <t>55,47</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>591</v>
+        <v>602</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>05.04.2019</t>
+          <t>05.07.2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bergen</t>
+          <t>Tøyen</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1679,20 +1679,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59,43</t>
+          <t>56,76</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>658</v>
+        <v>756</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>26.01.2025</t>
+          <t>05.07.2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Kristiansand</t>
+          <t>Tøyen</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1744,25 +1744,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Renate Knutsen</t>
+          <t>Silje Pettersen Olden</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.01,21</t>
+          <t>1.01,18</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>21.04.2023</t>
+          <t>02.07.2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bergen</t>
+          <t>Tøyen</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1779,25 +1779,25 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ylva S. Dyngeland</t>
+          <t>Renate Knutsen</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.01,53</t>
+          <t>1.01,21</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>593</v>
+        <v>602</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>01.03.2015</t>
+          <t>21.04.2023</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>Bergen</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1814,25 +1814,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Elise Nygård</t>
+          <t>Ylva S. Dyngeland</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.01,72</t>
+          <t>1.01,53</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>08.07.2017</t>
+          <t>01.03.2015</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Berlin</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1849,25 +1849,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Henriette Martinsen</t>
+          <t>Elise Nygård</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.01,81</t>
+          <t>1.01,72</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>13.07.2008</t>
+          <t>08.07.2017</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hamar</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1884,25 +1884,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Julie Mathilde Bjordal</t>
+          <t>Henriette Martinsen</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.02,15</t>
+          <t>1.01,81</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>575</v>
+        <v>585</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>08.07.2017</t>
+          <t>13.07.2008</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Hamar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1919,25 +1919,25 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Silje Pettersen Olden</t>
+          <t>Ada Fludal Osland</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1.02,35</t>
+          <t>1.02,07</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>570</v>
+        <v>578</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>06.07.2025</t>
+          <t>05.07.2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rud</t>
+          <t>Tøyen</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1954,25 +1954,25 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Karoline Volden</t>
+          <t>Julie Mathilde Bjordal</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.02,49</t>
+          <t>1.02,15</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>566</v>
+        <v>575</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>13.04.2018</t>
+          <t>08.07.2017</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bergen</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1989,25 +1989,25 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Tove Fludal Haugan</t>
+          <t>Karoline Volden</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1.02,85</t>
+          <t>1.02,49</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>556</v>
+        <v>566</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>12.06.2005</t>
+          <t>13.04.2018</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hamar</t>
+          <t>Bergen</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
